--- a/docs/analysis/risk_appetite/out/Shablon_mer_reagirovaniya_v1.0.xlsx
+++ b/docs/analysis/risk_appetite/out/Shablon_mer_reagirovaniya_v1.0.xlsx
@@ -618,7 +618,7 @@
     <row r="17" ht="45" customHeight="1">
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>ОГОВОРКА, КОТОРУЮ НАДО ЗНАТЬ. Две метрики CoR размечены предварительно: неизвестно, чем является их ряд — расходом за период или годовым уровнем. До ответа владельца расчёта зоны по ним недействительны. На листе «Пороги» они помечены.</t>
+          <t>ОГОВОРКА, КОТОРУЮ НАДО ЗНАТЬ. Две метрики CoR размечены замещающим методом (90-й процентиль значений за 36 месяцев) и предварительно: формула расчёта ряда не подтверждена. Граница красной зоны и пороги триггеров по ним — предложение. На листе «Пороги» они помечены.</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2604,11 @@
       <c r="G4" s="14" t="n">
         <v>10.42349048678484</v>
       </c>
-      <c r="H4" s="7" t="inlineStr"/>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>запас времени M(T)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
@@ -2616,7 +2620,7 @@
         <v>9</v>
       </c>
       <c r="C5" s="14" t="n">
-        <v>0.08015465622726432</v>
+        <v>0.08015465622726431</v>
       </c>
       <c r="D5" s="14" t="n">
         <v>8.794555349652521</v>
@@ -2630,7 +2634,11 @@
       <c r="G5" s="14" t="n">
         <v>0.2054446503474797</v>
       </c>
-      <c r="H5" s="7" t="inlineStr"/>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>запас времени M(T)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -2654,9 +2662,13 @@
         <v>0.1622304274914775</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>0.3244608549829551</v>
-      </c>
-      <c r="H6" s="7" t="inlineStr"/>
+        <v>0.324460854982955</v>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>запас времени M(T)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
@@ -2682,7 +2694,11 @@
       <c r="G7" s="14" t="n">
         <v>0.1322727518540728</v>
       </c>
-      <c r="H7" s="7" t="inlineStr"/>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>запас времени M(T)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
@@ -2708,7 +2724,11 @@
       <c r="G8" s="14" t="n">
         <v>0.218589439582695</v>
       </c>
-      <c r="H8" s="7" t="inlineStr"/>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
+          <t>запас времени M(T)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
@@ -2720,7 +2740,7 @@
         <v>15</v>
       </c>
       <c r="C9" s="14" t="n">
-        <v>0.1234365256155786</v>
+        <v>0.1234365256155785</v>
       </c>
       <c r="D9" s="14" t="n">
         <v>14.68361945470394</v>
@@ -2729,12 +2749,16 @@
         <v>14.84180972735197</v>
       </c>
       <c r="F9" s="14" t="n">
-        <v>0.1581902726480309</v>
+        <v>0.1581902726480308</v>
       </c>
       <c r="G9" s="14" t="n">
         <v>0.3163805452960617</v>
       </c>
-      <c r="H9" s="7" t="inlineStr"/>
+      <c r="H9" s="7" t="inlineStr">
+        <is>
+          <t>запас времени M(T)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
@@ -2760,7 +2784,11 @@
       <c r="G10" s="14" t="n">
         <v>0.3710279667626051</v>
       </c>
-      <c r="H10" s="7" t="inlineStr"/>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
+          <t>запас времени M(T)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
@@ -2786,7 +2814,11 @@
       <c r="G11" s="14" t="n">
         <v>0.2586694167203243</v>
       </c>
-      <c r="H11" s="7" t="inlineStr"/>
+      <c r="H11" s="7" t="inlineStr">
+        <is>
+          <t>запас времени M(T)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
@@ -2812,7 +2844,11 @@
       <c r="G12" s="14" t="n">
         <v>0.2559509793486734</v>
       </c>
-      <c r="H12" s="7" t="inlineStr"/>
+      <c r="H12" s="7" t="inlineStr">
+        <is>
+          <t>запас времени M(T)</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
@@ -2838,7 +2874,11 @@
       <c r="G13" s="14" t="n">
         <v>0.2666300276678822</v>
       </c>
-      <c r="H13" s="7" t="inlineStr"/>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>запас времени M(T)</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
@@ -2850,23 +2890,23 @@
         <v>3</v>
       </c>
       <c r="C14" s="14" t="n">
-        <v>1.281656509790512</v>
+        <v>1.281656509790511</v>
       </c>
       <c r="D14" s="14" t="n">
-        <v>-0.2850178132249175</v>
+        <v>0.5236724574800004</v>
       </c>
       <c r="E14" s="14" t="n">
-        <v>1.357491093387541</v>
+        <v>2.1650892752</v>
       </c>
       <c r="F14" s="14" t="n">
-        <v>1.642508906612459</v>
+        <v>0.8349107248000002</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>3.285017813224917</v>
+        <v>1.77543508026</v>
       </c>
       <c r="H14" s="15" t="inlineStr">
         <is>
-          <t>ПРЕДВАРИТЕЛЬНО — источник ряда не установлен</t>
+          <t>замещающий метод: 90-й процентиль значений. ПРЕДВАРИТЕЛЬНО — формула CoR не подтверждена; граница жёлтой/красной и T1/T2 — предложение</t>
         </is>
       </c>
     </row>
@@ -2883,20 +2923,20 @@
         <v>0.6623801859354517</v>
       </c>
       <c r="D15" s="14" t="n">
-        <v>1.802251271457397</v>
+        <v>0.2385719504200001</v>
       </c>
       <c r="E15" s="14" t="n">
-        <v>2.651125635728699</v>
+        <v>3.0386620116</v>
       </c>
       <c r="F15" s="14" t="n">
-        <v>0.8488743642713016</v>
+        <v>0.4613379884000002</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>1.697748728542603</v>
+        <v>1.32199011181</v>
       </c>
       <c r="H15" s="15" t="inlineStr">
         <is>
-          <t>ПРЕДВАРИТЕЛЬНО — источник ряда не установлен</t>
+          <t>замещающий метод: 90-й процентиль значений. ПРЕДВАРИТЕЛЬНО — формула CoR не подтверждена; граница жёлтой/красной и T1/T2 — предложение</t>
         </is>
       </c>
     </row>

--- a/docs/analysis/risk_appetite/out/Shablon_mer_reagirovaniya_v1.0.xlsx
+++ b/docs/analysis/risk_appetite/out/Shablon_mer_reagirovaniya_v1.0.xlsx
@@ -618,7 +618,7 @@
     <row r="17" ht="45" customHeight="1">
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>ОГОВОРКА, КОТОРУЮ НАДО ЗНАТЬ. Две метрики CoR размечены замещающим методом (90-й процентиль значений за 36 месяцев) и предварительно: формула расчёта ряда не подтверждена. Граница красной зоны и пороги триггеров по ним — предложение. На листе «Пороги» они помечены.</t>
+          <t>ОГОВОРКА, КОТОРУЮ НАДО ЗНАТЬ. Две метрики CoR размечены квантилем изменений по 29 обычным месяцам (без февраля–марта) и предварительно: формула расчёта ряда не подтверждена. На листе «Пороги» они помечены.</t>
         </is>
       </c>
     </row>
@@ -2893,20 +2893,20 @@
         <v>1.281656509790511</v>
       </c>
       <c r="D14" s="14" t="n">
-        <v>0.5236724574800004</v>
+        <v>1.5727452042</v>
       </c>
       <c r="E14" s="14" t="n">
-        <v>2.1650892752</v>
+        <v>2.28174503282</v>
       </c>
       <c r="F14" s="14" t="n">
-        <v>0.8349107248000002</v>
+        <v>0.7182549671799999</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>1.77543508026</v>
+        <v>1.4272547958</v>
       </c>
       <c r="H14" s="15" t="inlineStr">
         <is>
-          <t>замещающий метод: 90-й процентиль значений. ПРЕДВАРИТЕЛЬНО — формула CoR не подтверждена; граница жёлтой/красной и T1/T2 — предложение</t>
+          <t>квантиль изменений по 29 обычным месяцам (без фев–мар). ПРЕДВАРИТЕЛЬНО — формула расчёта CoR не подтверждена</t>
         </is>
       </c>
     </row>
@@ -2923,20 +2923,20 @@
         <v>0.6623801859354517</v>
       </c>
       <c r="D15" s="14" t="n">
-        <v>0.2385719504200001</v>
+        <v>2.4858615974</v>
       </c>
       <c r="E15" s="14" t="n">
-        <v>3.0386620116</v>
+        <v>3.12571530388</v>
       </c>
       <c r="F15" s="14" t="n">
-        <v>0.4613379884000002</v>
+        <v>0.3742846961199999</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>1.32199011181</v>
+        <v>1.0141384026</v>
       </c>
       <c r="H15" s="15" t="inlineStr">
         <is>
-          <t>замещающий метод: 90-й процентиль значений. ПРЕДВАРИТЕЛЬНО — формула CoR не подтверждена; граница жёлтой/красной и T1/T2 — предложение</t>
+          <t>квантиль изменений по 29 обычным месяцам (без фев–мар). ПРЕДВАРИТЕЛЬНО — формула расчёта CoR не подтверждена</t>
         </is>
       </c>
     </row>
